--- a/audit/docker_benchmark_reports/192.168.1.8_section5.xlsx
+++ b/audit/docker_benchmark_reports/192.168.1.8_section5.xlsx
@@ -788,7 +788,7 @@
     <row r="3" ht="16" customHeight="1">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Container Runtime Security  |  Host: Docker-2204-DA-AUTO  |  Docker: 29.4.3  |  OS: Ubuntu 22.04  |  2026-05-18T05:57:00Z</t>
+          <t>Container Runtime Security  |  Host: Docker-2204-DA-AUTO  |  Docker: 29.5.2  |  OS: Ubuntu 22.04  |  2026-05-21T18:50:27Z</t>
         </is>
       </c>
     </row>
@@ -1164,7 +1164,7 @@
       </c>
       <c r="G24" s="14" t="inlineStr">
         <is>
-          <t>Containers without correct restart policy (on-failure, max 5): c7a07d962204f0cb5b6f89a3c6813757704c8c80434155e55634ef875b575ca3:RestartPolicy=unless-stopped MaxRetry=0</t>
+          <t>Containers without correct restart policy (on-failure, max 5): ec30216769b1f0f215ee9993b33ce78c5a0b5337ea2444086f8baab724e177f4:RestartPolicy=unless-stopped MaxRetry=0</t>
         </is>
       </c>
     </row>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G35" s="11" t="inlineStr">
         <is>
-          <t>Containers missing no-new-privileges: c7a07d962204f0cb5b6f89a3c6813757704c8c80434155e55634ef875b575ca3</t>
+          <t>Containers missing no-new-privileges: ec30216769b1f0f215ee9993b33ce78c5a0b5337ea2444086f8baab724e177f4</t>
         </is>
       </c>
     </row>
@@ -1450,7 +1450,7 @@
       </c>
       <c r="G37" s="11" t="inlineStr">
         <is>
-          <t>Containers using latest tag or untagged image: c7a07d962204f0cb5b6f89a3c6813757704c8c80434155e55634ef875b575ca3:Image=nginx:latest</t>
+          <t>Containers using latest tag or untagged image: ec30216769b1f0f215ee9993b33ce78c5a0b5337ea2444086f8baab724e177f4:Image=nginx:latest</t>
         </is>
       </c>
     </row>
@@ -1814,7 +1814,7 @@
       </c>
       <c r="H3" s="21" t="inlineStr">
         <is>
-          <t>c7a07d962204f0cb5b6f89a3c6813757704c8c80434155e55634ef875b575ca3:AppArmorProfile=docker-default</t>
+          <t>ec30216769b1f0f215ee9993b33ce78c5a0b5337ea2444086f8baab724e177f4:AppArmorProfile=docker-default</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="H4" s="18" t="inlineStr">
         <is>
-          <t>c7a07d962204f0cb5b6f89a3c6813757704c8c80434155e55634ef875b575ca3:SecurityOpt=[label=level:TopSecret] MountLabel= ProcessLabel=</t>
+          <t>ec30216769b1f0f215ee9993b33ce78c5a0b5337ea2444086f8baab724e177f4:SecurityOpt=[label=level:TopSecret] MountLabel= ProcessLabel=</t>
         </is>
       </c>
     </row>
@@ -1888,7 +1888,7 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>c7a07d962204f0cb5b6f89a3c6813757704c8c80434155e55634ef875b575ca3:CapAdd=&lt;no value&gt; CapDrop=&lt;no value&gt;</t>
+          <t>ec30216769b1f0f215ee9993b33ce78c5a0b5337ea2444086f8baab724e177f4:CapAdd=&lt;no value&gt; CapDrop=&lt;no value&gt;</t>
         </is>
       </c>
     </row>
@@ -1925,7 +1925,7 @@
       </c>
       <c r="H6" s="18" t="inlineStr">
         <is>
-          <t>c7a07d962204f0cb5b6f89a3c6813757704c8c80434155e55634ef875b575ca3:Privileged=false</t>
+          <t>ec30216769b1f0f215ee9993b33ce78c5a0b5337ea2444086f8baab724e177f4:Privileged=false</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="H7" s="21" t="inlineStr">
         <is>
-          <t>c7a07d962204f0cb5b6f89a3c6813757704c8c80434155e55634ef875b575ca3:Volumes=[]</t>
+          <t>ec30216769b1f0f215ee9993b33ce78c5a0b5337ea2444086f8baab724e177f4:Volumes=[]</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="H9" s="21" t="inlineStr">
         <is>
-          <t>c7a07d962204f0cb5b6f89a3c6813757704c8c80434155e55634ef875b575ca3:Exposed={"80/tcp":{}} Published={"80/tcp":[{"HostIp":"127.0.0.1","HostPort":"8080"}]}</t>
+          <t>ec30216769b1f0f215ee9993b33ce78c5a0b5337ea2444086f8baab724e177f4:Exposed={"80/tcp":{}} Published={"80/tcp":[{"HostIp":"127.0.0.1","HostPort":"8080"}]}</t>
         </is>
       </c>
     </row>
@@ -2073,7 +2073,7 @@
       </c>
       <c r="H10" s="18" t="inlineStr">
         <is>
-          <t>c7a07d962204f0cb5b6f89a3c6813757704c8c80434155e55634ef875b575ca3:NetworkMode=secure-net</t>
+          <t>ec30216769b1f0f215ee9993b33ce78c5a0b5337ea2444086f8baab724e177f4:NetworkMode=secure-net</t>
         </is>
       </c>
     </row>
@@ -2110,7 +2110,7 @@
       </c>
       <c r="H11" s="21" t="inlineStr">
         <is>
-          <t>c7a07d962204f0cb5b6f89a3c6813757704c8c80434155e55634ef875b575ca3:Memory=268435456</t>
+          <t>ec30216769b1f0f215ee9993b33ce78c5a0b5337ea2444086f8baab724e177f4:Memory=268435456</t>
         </is>
       </c>
     </row>
@@ -2147,7 +2147,7 @@
       </c>
       <c r="H12" s="18" t="inlineStr">
         <is>
-          <t>c7a07d962204f0cb5b6f89a3c6813757704c8c80434155e55634ef875b575ca3:CpuShares=512</t>
+          <t>ec30216769b1f0f215ee9993b33ce78c5a0b5337ea2444086f8baab724e177f4:CpuShares=512</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="H13" s="21" t="inlineStr">
         <is>
-          <t>c7a07d962204f0cb5b6f89a3c6813757704c8c80434155e55634ef875b575ca3:ReadonlyRootfs=true</t>
+          <t>ec30216769b1f0f215ee9993b33ce78c5a0b5337ea2444086f8baab724e177f4:ReadonlyRootfs=true</t>
         </is>
       </c>
     </row>
@@ -2221,7 +2221,7 @@
       </c>
       <c r="H14" s="18" t="inlineStr">
         <is>
-          <t>c7a07d962204f0cb5b6f89a3c6813757704c8c80434155e55634ef875b575ca3:Ports={"80/tcp":[{"HostIp":"127.0.0.1","HostPort":"8080"}]}</t>
+          <t>ec30216769b1f0f215ee9993b33ce78c5a0b5337ea2444086f8baab724e177f4:Ports={"80/tcp":[{"HostIp":"127.0.0.1","HostPort":"8080"}]}</t>
         </is>
       </c>
     </row>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="F15" s="21" t="inlineStr">
         <is>
-          <t>Containers without correct restart policy (on-failure, max 5): c7a07d962204f0cb5b6f89a3c6813757704c8c80434155e55634ef875b575ca3:RestartPolicy=unless-stopped MaxRetry=0</t>
+          <t>Containers without correct restart policy (on-failure, max 5): ec30216769b1f0f215ee9993b33ce78c5a0b5337ea2444086f8baab724e177f4:RestartPolicy=unless-stopped MaxRetry=0</t>
         </is>
       </c>
       <c r="G15" s="21" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="H15" s="21" t="inlineStr">
         <is>
-          <t>c7a07d962204f0cb5b6f89a3c6813757704c8c80434155e55634ef875b575ca3:RestartPolicy=unless-stopped MaxRetry=0</t>
+          <t>ec30216769b1f0f215ee9993b33ce78c5a0b5337ea2444086f8baab724e177f4:RestartPolicy=unless-stopped MaxRetry=0</t>
         </is>
       </c>
     </row>
@@ -2295,7 +2295,7 @@
       </c>
       <c r="H16" s="18" t="inlineStr">
         <is>
-          <t>c7a07d962204f0cb5b6f89a3c6813757704c8c80434155e55634ef875b575ca3:PidMode=</t>
+          <t>ec30216769b1f0f215ee9993b33ce78c5a0b5337ea2444086f8baab724e177f4:PidMode=</t>
         </is>
       </c>
     </row>
@@ -2332,7 +2332,7 @@
       </c>
       <c r="H17" s="21" t="inlineStr">
         <is>
-          <t>c7a07d962204f0cb5b6f89a3c6813757704c8c80434155e55634ef875b575ca3:IpcMode=private</t>
+          <t>ec30216769b1f0f215ee9993b33ce78c5a0b5337ea2444086f8baab724e177f4:IpcMode=private</t>
         </is>
       </c>
     </row>
@@ -2369,7 +2369,7 @@
       </c>
       <c r="H18" s="18" t="inlineStr">
         <is>
-          <t>c7a07d962204f0cb5b6f89a3c6813757704c8c80434155e55634ef875b575ca3:Devices=null</t>
+          <t>ec30216769b1f0f215ee9993b33ce78c5a0b5337ea2444086f8baab724e177f4:Devices=null</t>
         </is>
       </c>
     </row>
@@ -2406,7 +2406,7 @@
       </c>
       <c r="H19" s="21" t="inlineStr">
         <is>
-          <t>c7a07d962204f0cb5b6f89a3c6813757704c8c80434155e55634ef875b575ca3:Ulimits=[{"Hard":1024,"Name":"nofile","Soft":1024}]</t>
+          <t>ec30216769b1f0f215ee9993b33ce78c5a0b5337ea2444086f8baab724e177f4:Ulimits=[{"Hard":1024,"Name":"nofile","Soft":1024}]</t>
         </is>
       </c>
     </row>
@@ -2443,7 +2443,7 @@
       </c>
       <c r="H20" s="18" t="inlineStr">
         <is>
-          <t>c7a07d962204f0cb5b6f89a3c6813757704c8c80434155e55634ef875b575ca3:Mounts=[]</t>
+          <t>ec30216769b1f0f215ee9993b33ce78c5a0b5337ea2444086f8baab724e177f4:Mounts=[]</t>
         </is>
       </c>
     </row>
@@ -2480,7 +2480,7 @@
       </c>
       <c r="H21" s="21" t="inlineStr">
         <is>
-          <t>c7a07d962204f0cb5b6f89a3c6813757704c8c80434155e55634ef875b575ca3:UTSMode=</t>
+          <t>ec30216769b1f0f215ee9993b33ce78c5a0b5337ea2444086f8baab724e177f4:UTSMode=</t>
         </is>
       </c>
     </row>
@@ -2517,7 +2517,7 @@
       </c>
       <c r="H22" s="18" t="inlineStr">
         <is>
-          <t>c7a07d962204f0cb5b6f89a3c6813757704c8c80434155e55634ef875b575ca3:SecurityOpt=["label=level:TopSecret"]</t>
+          <t>ec30216769b1f0f215ee9993b33ce78c5a0b5337ea2444086f8baab724e177f4:SecurityOpt=["label=level:TopSecret"]</t>
         </is>
       </c>
     </row>
@@ -2620,7 +2620,7 @@
       </c>
       <c r="H25" s="21" t="inlineStr">
         <is>
-          <t>c7a07d962204f0cb5b6f89a3c6813757704c8c80434155e55634ef875b575ca3:CgroupParent=</t>
+          <t>ec30216769b1f0f215ee9993b33ce78c5a0b5337ea2444086f8baab724e177f4:CgroupParent=</t>
         </is>
       </c>
     </row>
@@ -2647,7 +2647,7 @@
       </c>
       <c r="F26" s="18" t="inlineStr">
         <is>
-          <t>Containers missing no-new-privileges: c7a07d962204f0cb5b6f89a3c6813757704c8c80434155e55634ef875b575ca3</t>
+          <t>Containers missing no-new-privileges: ec30216769b1f0f215ee9993b33ce78c5a0b5337ea2444086f8baab724e177f4</t>
         </is>
       </c>
       <c r="G26" s="18" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="H26" s="18" t="inlineStr">
         <is>
-          <t>c7a07d962204f0cb5b6f89a3c6813757704c8c80434155e55634ef875b575ca3:SecurityOpt=["label=level:TopSecret"]</t>
+          <t>ec30216769b1f0f215ee9993b33ce78c5a0b5337ea2444086f8baab724e177f4:SecurityOpt=["label=level:TopSecret"]</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="H27" s="21" t="inlineStr">
         <is>
-          <t>c7a07d962204f0cb5b6f89a3c6813757704c8c80434155e55634ef875b575ca3:Health=unhealthy</t>
+          <t>ec30216769b1f0f215ee9993b33ce78c5a0b5337ea2444086f8baab724e177f4:Health=starting</t>
         </is>
       </c>
     </row>
@@ -2721,7 +2721,7 @@
       </c>
       <c r="F28" s="18" t="inlineStr">
         <is>
-          <t>Containers using latest tag or untagged image: c7a07d962204f0cb5b6f89a3c6813757704c8c80434155e55634ef875b575ca3:Image=nginx:latest</t>
+          <t>Containers using latest tag or untagged image: ec30216769b1f0f215ee9993b33ce78c5a0b5337ea2444086f8baab724e177f4:Image=nginx:latest</t>
         </is>
       </c>
       <c r="G28" s="18" t="inlineStr">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="H28" s="18" t="inlineStr">
         <is>
-          <t>c7a07d962204f0cb5b6f89a3c6813757704c8c80434155e55634ef875b575ca3:Image=nginx:latest</t>
+          <t>ec30216769b1f0f215ee9993b33ce78c5a0b5337ea2444086f8baab724e177f4:Image=nginx:latest</t>
         </is>
       </c>
     </row>
@@ -2768,7 +2768,7 @@
       </c>
       <c r="H29" s="21" t="inlineStr">
         <is>
-          <t>c7a07d962204f0cb5b6f89a3c6813757704c8c80434155e55634ef875b575ca3:PidsLimit=100</t>
+          <t>ec30216769b1f0f215ee9993b33ce78c5a0b5337ea2444086f8baab724e177f4:PidsLimit=100</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="H30" s="18" t="inlineStr">
         <is>
-          <t>c7a07d962204f0cb5b6f89a3c6813757704c8c80434155e55634ef875b575ca3:Networks={"secure-net":{"Aliases":null,"DNSNames":["my_container","c7a07d962204"],"DriverOpts":null,"EndpointID":"c68bb358dda7d2e61743b54d80d397da87c3f0790cc68594b0119594fa5c575d","Gateway":"172.18.0.1","GlobalIPv6Address":"","GlobalIPv6PrefixLen":0,"GwPriority":0,"IPAMConfig":null,"IPAddress":"172.18.0.2","IPPrefixLen":16,"IPv6Gateway":"","Links":null,"MacAddress":"02:5b:8a:bd:dc:0d","NetworkID":"89cca936b62f5f456209577aa4aae8c9dd3e1c95257b099a1678ba6b87502d9b"}}</t>
+          <t>ec30216769b1f0f215ee9993b33ce78c5a0b5337ea2444086f8baab724e177f4:Networks={"secure-net":{"Aliases":null,"DNSNames":["my_container","ec30216769b1"],"DriverOpts":null,"EndpointID":"426ab35fa1777c120407914745a0d63d8d9f518372f94fb484ad66d3865e26c1","Gateway":"172.19.0.1","GlobalIPv6Address":"","GlobalIPv6PrefixLen":0,"GwPriority":0,"IPAMConfig":null,"IPAddress":"172.19.0.2","IPPrefixLen":16,"IPv6Gateway":"","Links":null,"MacAddress":"82:99:cd:15:df:33","NetworkID":"3eb35a73339562ab43c26274ef570d0fef6953995aaee7ff82dbe519a7cf8f1f"}}</t>
         </is>
       </c>
     </row>
@@ -2842,7 +2842,7 @@
       </c>
       <c r="H31" s="21" t="inlineStr">
         <is>
-          <t>c7a07d962204f0cb5b6f89a3c6813757704c8c80434155e55634ef875b575ca3:UsernsMode=</t>
+          <t>ec30216769b1f0f215ee9993b33ce78c5a0b5337ea2444086f8baab724e177f4:UsernsMode=</t>
         </is>
       </c>
     </row>
@@ -2879,7 +2879,7 @@
       </c>
       <c r="H32" s="18" t="inlineStr">
         <is>
-          <t>c7a07d962204f0cb5b6f89a3c6813757704c8c80434155e55634ef875b575ca3:Mounts=[]</t>
+          <t>ec30216769b1f0f215ee9993b33ce78c5a0b5337ea2444086f8baab724e177f4:Mounts=[]</t>
         </is>
       </c>
     </row>

--- a/audit/docker_benchmark_reports/192.168.1.8_section5.xlsx
+++ b/audit/docker_benchmark_reports/192.168.1.8_section5.xlsx
@@ -788,7 +788,7 @@
     <row r="3" ht="16" customHeight="1">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Container Runtime Security  |  Host: Docker-2204-DA-AUTO  |  Docker: 29.5.2  |  OS: Ubuntu 22.04  |  2026-05-21T18:50:27Z</t>
+          <t>Container Runtime Security  |  Host: Docker-2204-DA-AUTO  |  Docker: 29.5.2  |  OS: Ubuntu 22.04  |  2026-05-28T13:05:03Z</t>
         </is>
       </c>
     </row>
@@ -1164,7 +1164,7 @@
       </c>
       <c r="G24" s="14" t="inlineStr">
         <is>
-          <t>Containers without correct restart policy (on-failure, max 5): ec30216769b1f0f215ee9993b33ce78c5a0b5337ea2444086f8baab724e177f4:RestartPolicy=unless-stopped MaxRetry=0</t>
+          <t>Containers without correct restart policy (on-failure, max 5): 604a9ddde61b9aa5c271028df05ff7a2d759b4b3e6cd7cc1ddfc66a1cf615278:RestartPolicy=unless-stopped MaxRetry=0</t>
         </is>
       </c>
     </row>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G35" s="11" t="inlineStr">
         <is>
-          <t>Containers missing no-new-privileges: ec30216769b1f0f215ee9993b33ce78c5a0b5337ea2444086f8baab724e177f4</t>
+          <t>Containers missing no-new-privileges: 604a9ddde61b9aa5c271028df05ff7a2d759b4b3e6cd7cc1ddfc66a1cf615278</t>
         </is>
       </c>
     </row>
@@ -1450,7 +1450,7 @@
       </c>
       <c r="G37" s="11" t="inlineStr">
         <is>
-          <t>Containers using latest tag or untagged image: ec30216769b1f0f215ee9993b33ce78c5a0b5337ea2444086f8baab724e177f4:Image=nginx:latest</t>
+          <t>Containers using latest tag or untagged image: 604a9ddde61b9aa5c271028df05ff7a2d759b4b3e6cd7cc1ddfc66a1cf615278:Image=nginx:latest</t>
         </is>
       </c>
     </row>
@@ -1814,7 +1814,7 @@
       </c>
       <c r="H3" s="21" t="inlineStr">
         <is>
-          <t>ec30216769b1f0f215ee9993b33ce78c5a0b5337ea2444086f8baab724e177f4:AppArmorProfile=docker-default</t>
+          <t>604a9ddde61b9aa5c271028df05ff7a2d759b4b3e6cd7cc1ddfc66a1cf615278:AppArmorProfile=docker-default</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="H4" s="18" t="inlineStr">
         <is>
-          <t>ec30216769b1f0f215ee9993b33ce78c5a0b5337ea2444086f8baab724e177f4:SecurityOpt=[label=level:TopSecret] MountLabel= ProcessLabel=</t>
+          <t>604a9ddde61b9aa5c271028df05ff7a2d759b4b3e6cd7cc1ddfc66a1cf615278:SecurityOpt=[label=level:TopSecret] MountLabel= ProcessLabel=</t>
         </is>
       </c>
     </row>
@@ -1888,7 +1888,7 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>ec30216769b1f0f215ee9993b33ce78c5a0b5337ea2444086f8baab724e177f4:CapAdd=&lt;no value&gt; CapDrop=&lt;no value&gt;</t>
+          <t>604a9ddde61b9aa5c271028df05ff7a2d759b4b3e6cd7cc1ddfc66a1cf615278:CapAdd=&lt;no value&gt; CapDrop=&lt;no value&gt;</t>
         </is>
       </c>
     </row>
@@ -1925,7 +1925,7 @@
       </c>
       <c r="H6" s="18" t="inlineStr">
         <is>
-          <t>ec30216769b1f0f215ee9993b33ce78c5a0b5337ea2444086f8baab724e177f4:Privileged=false</t>
+          <t>604a9ddde61b9aa5c271028df05ff7a2d759b4b3e6cd7cc1ddfc66a1cf615278:Privileged=false</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="H7" s="21" t="inlineStr">
         <is>
-          <t>ec30216769b1f0f215ee9993b33ce78c5a0b5337ea2444086f8baab724e177f4:Volumes=[]</t>
+          <t>604a9ddde61b9aa5c271028df05ff7a2d759b4b3e6cd7cc1ddfc66a1cf615278:Volumes=[]</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="H9" s="21" t="inlineStr">
         <is>
-          <t>ec30216769b1f0f215ee9993b33ce78c5a0b5337ea2444086f8baab724e177f4:Exposed={"80/tcp":{}} Published={"80/tcp":[{"HostIp":"127.0.0.1","HostPort":"8080"}]}</t>
+          <t>604a9ddde61b9aa5c271028df05ff7a2d759b4b3e6cd7cc1ddfc66a1cf615278:Exposed={"80/tcp":{}} Published={"80/tcp":[{"HostIp":"127.0.0.1","HostPort":"8080"}]}</t>
         </is>
       </c>
     </row>
@@ -2073,7 +2073,7 @@
       </c>
       <c r="H10" s="18" t="inlineStr">
         <is>
-          <t>ec30216769b1f0f215ee9993b33ce78c5a0b5337ea2444086f8baab724e177f4:NetworkMode=secure-net</t>
+          <t>604a9ddde61b9aa5c271028df05ff7a2d759b4b3e6cd7cc1ddfc66a1cf615278:NetworkMode=secure-net</t>
         </is>
       </c>
     </row>
@@ -2110,7 +2110,7 @@
       </c>
       <c r="H11" s="21" t="inlineStr">
         <is>
-          <t>ec30216769b1f0f215ee9993b33ce78c5a0b5337ea2444086f8baab724e177f4:Memory=268435456</t>
+          <t>604a9ddde61b9aa5c271028df05ff7a2d759b4b3e6cd7cc1ddfc66a1cf615278:Memory=268435456</t>
         </is>
       </c>
     </row>
@@ -2147,7 +2147,7 @@
       </c>
       <c r="H12" s="18" t="inlineStr">
         <is>
-          <t>ec30216769b1f0f215ee9993b33ce78c5a0b5337ea2444086f8baab724e177f4:CpuShares=512</t>
+          <t>604a9ddde61b9aa5c271028df05ff7a2d759b4b3e6cd7cc1ddfc66a1cf615278:CpuShares=512</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="H13" s="21" t="inlineStr">
         <is>
-          <t>ec30216769b1f0f215ee9993b33ce78c5a0b5337ea2444086f8baab724e177f4:ReadonlyRootfs=true</t>
+          <t>604a9ddde61b9aa5c271028df05ff7a2d759b4b3e6cd7cc1ddfc66a1cf615278:ReadonlyRootfs=true</t>
         </is>
       </c>
     </row>
@@ -2221,7 +2221,7 @@
       </c>
       <c r="H14" s="18" t="inlineStr">
         <is>
-          <t>ec30216769b1f0f215ee9993b33ce78c5a0b5337ea2444086f8baab724e177f4:Ports={"80/tcp":[{"HostIp":"127.0.0.1","HostPort":"8080"}]}</t>
+          <t>604a9ddde61b9aa5c271028df05ff7a2d759b4b3e6cd7cc1ddfc66a1cf615278:Ports={"80/tcp":[{"HostIp":"127.0.0.1","HostPort":"8080"}]}</t>
         </is>
       </c>
     </row>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="F15" s="21" t="inlineStr">
         <is>
-          <t>Containers without correct restart policy (on-failure, max 5): ec30216769b1f0f215ee9993b33ce78c5a0b5337ea2444086f8baab724e177f4:RestartPolicy=unless-stopped MaxRetry=0</t>
+          <t>Containers without correct restart policy (on-failure, max 5): 604a9ddde61b9aa5c271028df05ff7a2d759b4b3e6cd7cc1ddfc66a1cf615278:RestartPolicy=unless-stopped MaxRetry=0</t>
         </is>
       </c>
       <c r="G15" s="21" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="H15" s="21" t="inlineStr">
         <is>
-          <t>ec30216769b1f0f215ee9993b33ce78c5a0b5337ea2444086f8baab724e177f4:RestartPolicy=unless-stopped MaxRetry=0</t>
+          <t>604a9ddde61b9aa5c271028df05ff7a2d759b4b3e6cd7cc1ddfc66a1cf615278:RestartPolicy=unless-stopped MaxRetry=0</t>
         </is>
       </c>
     </row>
@@ -2295,7 +2295,7 @@
       </c>
       <c r="H16" s="18" t="inlineStr">
         <is>
-          <t>ec30216769b1f0f215ee9993b33ce78c5a0b5337ea2444086f8baab724e177f4:PidMode=</t>
+          <t>604a9ddde61b9aa5c271028df05ff7a2d759b4b3e6cd7cc1ddfc66a1cf615278:PidMode=</t>
         </is>
       </c>
     </row>
@@ -2332,7 +2332,7 @@
       </c>
       <c r="H17" s="21" t="inlineStr">
         <is>
-          <t>ec30216769b1f0f215ee9993b33ce78c5a0b5337ea2444086f8baab724e177f4:IpcMode=private</t>
+          <t>604a9ddde61b9aa5c271028df05ff7a2d759b4b3e6cd7cc1ddfc66a1cf615278:IpcMode=private</t>
         </is>
       </c>
     </row>
@@ -2369,7 +2369,7 @@
       </c>
       <c r="H18" s="18" t="inlineStr">
         <is>
-          <t>ec30216769b1f0f215ee9993b33ce78c5a0b5337ea2444086f8baab724e177f4:Devices=null</t>
+          <t>604a9ddde61b9aa5c271028df05ff7a2d759b4b3e6cd7cc1ddfc66a1cf615278:Devices=null</t>
         </is>
       </c>
     </row>
@@ -2406,7 +2406,7 @@
       </c>
       <c r="H19" s="21" t="inlineStr">
         <is>
-          <t>ec30216769b1f0f215ee9993b33ce78c5a0b5337ea2444086f8baab724e177f4:Ulimits=[{"Hard":1024,"Name":"nofile","Soft":1024}]</t>
+          <t>604a9ddde61b9aa5c271028df05ff7a2d759b4b3e6cd7cc1ddfc66a1cf615278:Ulimits=[{"Hard":1024,"Name":"nofile","Soft":1024}]</t>
         </is>
       </c>
     </row>
@@ -2443,7 +2443,7 @@
       </c>
       <c r="H20" s="18" t="inlineStr">
         <is>
-          <t>ec30216769b1f0f215ee9993b33ce78c5a0b5337ea2444086f8baab724e177f4:Mounts=[]</t>
+          <t>604a9ddde61b9aa5c271028df05ff7a2d759b4b3e6cd7cc1ddfc66a1cf615278:Mounts=[]</t>
         </is>
       </c>
     </row>
@@ -2480,7 +2480,7 @@
       </c>
       <c r="H21" s="21" t="inlineStr">
         <is>
-          <t>ec30216769b1f0f215ee9993b33ce78c5a0b5337ea2444086f8baab724e177f4:UTSMode=</t>
+          <t>604a9ddde61b9aa5c271028df05ff7a2d759b4b3e6cd7cc1ddfc66a1cf615278:UTSMode=</t>
         </is>
       </c>
     </row>
@@ -2517,7 +2517,7 @@
       </c>
       <c r="H22" s="18" t="inlineStr">
         <is>
-          <t>ec30216769b1f0f215ee9993b33ce78c5a0b5337ea2444086f8baab724e177f4:SecurityOpt=["label=level:TopSecret"]</t>
+          <t>604a9ddde61b9aa5c271028df05ff7a2d759b4b3e6cd7cc1ddfc66a1cf615278:SecurityOpt=["label=level:TopSecret"]</t>
         </is>
       </c>
     </row>
@@ -2620,7 +2620,7 @@
       </c>
       <c r="H25" s="21" t="inlineStr">
         <is>
-          <t>ec30216769b1f0f215ee9993b33ce78c5a0b5337ea2444086f8baab724e177f4:CgroupParent=</t>
+          <t>604a9ddde61b9aa5c271028df05ff7a2d759b4b3e6cd7cc1ddfc66a1cf615278:CgroupParent=</t>
         </is>
       </c>
     </row>
@@ -2647,7 +2647,7 @@
       </c>
       <c r="F26" s="18" t="inlineStr">
         <is>
-          <t>Containers missing no-new-privileges: ec30216769b1f0f215ee9993b33ce78c5a0b5337ea2444086f8baab724e177f4</t>
+          <t>Containers missing no-new-privileges: 604a9ddde61b9aa5c271028df05ff7a2d759b4b3e6cd7cc1ddfc66a1cf615278</t>
         </is>
       </c>
       <c r="G26" s="18" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="H26" s="18" t="inlineStr">
         <is>
-          <t>ec30216769b1f0f215ee9993b33ce78c5a0b5337ea2444086f8baab724e177f4:SecurityOpt=["label=level:TopSecret"]</t>
+          <t>604a9ddde61b9aa5c271028df05ff7a2d759b4b3e6cd7cc1ddfc66a1cf615278:SecurityOpt=["label=level:TopSecret"]</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="H27" s="21" t="inlineStr">
         <is>
-          <t>ec30216769b1f0f215ee9993b33ce78c5a0b5337ea2444086f8baab724e177f4:Health=starting</t>
+          <t>604a9ddde61b9aa5c271028df05ff7a2d759b4b3e6cd7cc1ddfc66a1cf615278:Health=starting</t>
         </is>
       </c>
     </row>
@@ -2721,7 +2721,7 @@
       </c>
       <c r="F28" s="18" t="inlineStr">
         <is>
-          <t>Containers using latest tag or untagged image: ec30216769b1f0f215ee9993b33ce78c5a0b5337ea2444086f8baab724e177f4:Image=nginx:latest</t>
+          <t>Containers using latest tag or untagged image: 604a9ddde61b9aa5c271028df05ff7a2d759b4b3e6cd7cc1ddfc66a1cf615278:Image=nginx:latest</t>
         </is>
       </c>
       <c r="G28" s="18" t="inlineStr">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="H28" s="18" t="inlineStr">
         <is>
-          <t>ec30216769b1f0f215ee9993b33ce78c5a0b5337ea2444086f8baab724e177f4:Image=nginx:latest</t>
+          <t>604a9ddde61b9aa5c271028df05ff7a2d759b4b3e6cd7cc1ddfc66a1cf615278:Image=nginx:latest</t>
         </is>
       </c>
     </row>
@@ -2768,7 +2768,7 @@
       </c>
       <c r="H29" s="21" t="inlineStr">
         <is>
-          <t>ec30216769b1f0f215ee9993b33ce78c5a0b5337ea2444086f8baab724e177f4:PidsLimit=100</t>
+          <t>604a9ddde61b9aa5c271028df05ff7a2d759b4b3e6cd7cc1ddfc66a1cf615278:PidsLimit=100</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="H30" s="18" t="inlineStr">
         <is>
-          <t>ec30216769b1f0f215ee9993b33ce78c5a0b5337ea2444086f8baab724e177f4:Networks={"secure-net":{"Aliases":null,"DNSNames":["my_container","ec30216769b1"],"DriverOpts":null,"EndpointID":"426ab35fa1777c120407914745a0d63d8d9f518372f94fb484ad66d3865e26c1","Gateway":"172.19.0.1","GlobalIPv6Address":"","GlobalIPv6PrefixLen":0,"GwPriority":0,"IPAMConfig":null,"IPAddress":"172.19.0.2","IPPrefixLen":16,"IPv6Gateway":"","Links":null,"MacAddress":"82:99:cd:15:df:33","NetworkID":"3eb35a73339562ab43c26274ef570d0fef6953995aaee7ff82dbe519a7cf8f1f"}}</t>
+          <t>604a9ddde61b9aa5c271028df05ff7a2d759b4b3e6cd7cc1ddfc66a1cf615278:Networks={"secure-net":{"Aliases":null,"DNSNames":["my_container","604a9ddde61b"],"DriverOpts":null,"EndpointID":"46abd8505c20e7e49f384a45ee5a6a5fdd20aa60698da81fe7193bcf137e4f68","Gateway":"172.18.0.1","GlobalIPv6Address":"","GlobalIPv6PrefixLen":0,"GwPriority":0,"IPAMConfig":null,"IPAddress":"172.18.0.2","IPPrefixLen":16,"IPv6Gateway":"","Links":null,"MacAddress":"f2:05:bd:c3:5b:28","NetworkID":"a61d2cc4c450ee56835a0e49b188cfda9605d00bfa8a53a4492df463b5df2fa7"}}</t>
         </is>
       </c>
     </row>
@@ -2842,7 +2842,7 @@
       </c>
       <c r="H31" s="21" t="inlineStr">
         <is>
-          <t>ec30216769b1f0f215ee9993b33ce78c5a0b5337ea2444086f8baab724e177f4:UsernsMode=</t>
+          <t>604a9ddde61b9aa5c271028df05ff7a2d759b4b3e6cd7cc1ddfc66a1cf615278:UsernsMode=</t>
         </is>
       </c>
     </row>
@@ -2879,7 +2879,7 @@
       </c>
       <c r="H32" s="18" t="inlineStr">
         <is>
-          <t>ec30216769b1f0f215ee9993b33ce78c5a0b5337ea2444086f8baab724e177f4:Mounts=[]</t>
+          <t>604a9ddde61b9aa5c271028df05ff7a2d759b4b3e6cd7cc1ddfc66a1cf615278:Mounts=[]</t>
         </is>
       </c>
     </row>
